--- a/01_Transporte_EMTU_limpio.xlsx
+++ b/01_Transporte_EMTU_limpio.xlsx
@@ -1009,16 +1009,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nulos</t>
+          <t>Tipos</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>'pasajeros' imputados con la mediana (56.5)</t>
+          <t>'fecha' convertida a datetime</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -1029,11 +1029,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>'temperatura' imputados con la mediana (16.9)</t>
+          <t>'pasajeros' rellenos con la mediana (56.5)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>'mantenimiento_dias' imputados con la mediana (11.0)</t>
+          <t>'temperatura' rellenos con la mediana (16.9)</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1054,12 +1054,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Outliers</t>
+          <t>Nulos</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>'pasajeros' recortados a [38.6, 75.6] (antes=[180.0], después=[75.625])</t>
+          <t>'mantenimiento_dias' rellenos con la mediana (11.0)</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1069,33 +1069,33 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Filas</t>
+          <t>Outliers</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>total: originales -&gt; limpias</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>13 -&gt; 12</t>
-        </is>
+          <t>'pasajeros' recortados a [38.6, 75.6] (antes=[180.0], después=[75.625])</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tipos</t>
+          <t>Filas</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>'fecha' convertida a fecha (datetime)</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>12</v>
+          <t>total: originales -&gt; limpias</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>13 -&gt; 12</t>
+        </is>
       </c>
     </row>
   </sheetData>
